--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -4561,7 +4561,7 @@
         <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -375,7 +375,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ImmunizationRecommendation|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -600,7 +600,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -830,7 +830,7 @@
     <t>JP_DiagnosticReportCategory_VSの中から「LP7796-8」（Endoscopy（内視鏡））を指定する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS|1.1.0</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.id</t>
@@ -891,7 +891,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_Endoscopy_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_Endoscopy_VS|1.1.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -913,7 +913,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -948,7 +948,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1050,7 +1050,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1085,7 +1085,7 @@
 Reported by</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1104,7 +1104,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1130,7 +1130,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Endoscopy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Endoscopy|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1155,7 +1155,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Endoscopy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Endoscopy|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1239,7 +1239,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Media_Endoscopy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Media_Endoscopy|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1286,7 +1286,7 @@
     <t>JED Project（https://jedproject.jges.net/）が対象とする検査種別については、指定された質的診断コードを使用することを強く推奨する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConclusionCodesJed_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConclusionCodesJed_VS|1.1.0</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1643,7 +1643,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="178.02734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="212.125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1658,7 +1658,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="47.21484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.26953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -375,7 +375,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ImmunizationRecommendation|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -600,7 +600,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -830,7 +830,7 @@
     <t>JP_DiagnosticReportCategory_VSの中から「LP7796-8」（Endoscopy（内視鏡））を指定する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.id</t>
@@ -891,7 +891,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_Endoscopy_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_Endoscopy_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -913,7 +913,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -948,7 +948,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -1050,7 +1050,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
 </t>
   </si>
   <si>
@@ -1085,7 +1085,7 @@
 Reported by</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -1104,7 +1104,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -1130,7 +1130,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Endoscopy|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Endoscopy)
 </t>
   </si>
   <si>
@@ -1155,7 +1155,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Endoscopy|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Endoscopy)
 </t>
   </si>
   <si>
@@ -1239,7 +1239,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Media_Endoscopy|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Media_Endoscopy)
 </t>
   </si>
   <si>
@@ -1286,7 +1286,7 @@
     <t>JED Project（https://jedproject.jges.net/）が対象とする検査種別については、指定された質的診断コードを使用することを強く推奨する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConclusionCodesJed_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConclusionCodesJed_VS</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1643,7 +1643,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="212.125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="178.02734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1658,7 +1658,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="47.21484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.26953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
